--- a/data/trans_camb/IP1006-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,47</t>
+          <t>0,0; 2,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,33</t>
+          <t>0,0; 2,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 3,9</t>
+          <t>-0,49; 4,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,53</t>
+          <t>-0,94; 1,56</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,24</t>
+          <t>-0,04; 2,37</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,22</t>
+          <t>-0,49; 1,23</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 0,67</t>
+          <t>-1,67; 0,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 1,98</t>
+          <t>-1,03; 1,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 1,48</t>
+          <t>-0,69; 1,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,8</t>
+          <t>-1,02; 0,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,83; 0,63</t>
+          <t>-0,82; 0,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,02</t>
+          <t>-0,64; 0,99</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,12; 0,0</t>
+          <t>-2,04; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,55; 0,0</t>
+          <t>-1,92; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,48</t>
+          <t>0,0; 2,05</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,92</t>
+          <t>0,0; 1,69</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,54</t>
+          <t>-0,55; 0,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,59</t>
+          <t>-0,37; 0,6</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 0,0</t>
+          <t>-2,09; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,42; 0,0</t>
+          <t>-1,78; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,79</t>
+          <t>-0,67; 1,86</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,53; 0,0</t>
+          <t>-1,61; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,74</t>
+          <t>-0,66; 0,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 0,0</t>
+          <t>-1,0; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,28</t>
+          <t>-0,64; 0,28</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,53</t>
+          <t>-0,5; 0,5</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,14; 1,22</t>
+          <t>-0,06; 1,21</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,51; 0,42</t>
+          <t>-0,5; 0,37</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 0,59</t>
+          <t>-0,21; 0,58</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,37</t>
+          <t>-0,34; 0,32</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-88,57; 484,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-54,75; 1173,73</t>
+          <t>-43,27; 1169,96</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-41,77; 337,14</t>
+          <t>-54,41; 346,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,43; 237,81</t>
+          <t>-71,35; 206,39</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Habitat-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,9</t>
+          <t>0,0; 2,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,94</t>
+          <t>0,0; 2,13</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 4,08</t>
+          <t>-0,5; 3,74</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 1,56</t>
+          <t>-1,37; 1,51</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,37</t>
+          <t>-0,09; 2,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,23</t>
+          <t>-0,49; 1,11</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 0,67</t>
+          <t>-1,66; 0,67</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,03; 1,86</t>
+          <t>-1,02; 1,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,47</t>
+          <t>-0,69; 1,2</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 0,56</t>
+          <t>-1,29; 0,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 0,76</t>
+          <t>-0,96; 0,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,99</t>
+          <t>-0,69; 1,04</t>
         </is>
       </c>
     </row>
@@ -943,27 +943,27 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 0,0</t>
+          <t>-1,91; 0,0</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,92; 0,0</t>
+          <t>-1,9; 0,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,05</t>
+          <t>0,0; 1,77</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,69</t>
+          <t>0,0; 2,44</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 0,37</t>
+          <t>-0,73; 0,37</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 0,0</t>
+          <t>-2,17; 0,0</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 0,0</t>
+          <t>-1,88; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 1,86</t>
+          <t>-0,68; 1,72</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 0,0</t>
+          <t>-1,69; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 0,76</t>
+          <t>-0,63; 0,73</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 0,0</t>
+          <t>-1,19; 0,0</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,28</t>
+          <t>-0,64; 0,21</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,5</t>
+          <t>-0,5; 0,56</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 1,21</t>
+          <t>-0,03; 1,25</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,37</t>
+          <t>-0,5; 0,41</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,21; 0,58</t>
+          <t>-0,2; 0,6</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,34; 0,32</t>
+          <t>-0,38; 0,32</t>
         </is>
       </c>
     </row>
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-88,57; 484,36</t>
+          <t>-87,51; 541,62</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-43,27; 1169,96</t>
+          <t>-37,87; 1571,15</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-54,41; 346,45</t>
+          <t>-46,99; 374,3</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-71,35; 206,39</t>
+          <t>-72,96; 223,54</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP1006-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP1006-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>1,18</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0,03</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0,48</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>0,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,18</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,03</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,48</t>
+          <t>-0,49; 3,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,13</t>
+          <t>-0,95; 1,53</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 3,74</t>
+          <t>0,0; 2,47</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 1,51</t>
+          <t>0,0; 2,33</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 2,45</t>
+          <t>-0,04; 2,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-0,49; 1,11</t>
+          <t>-0,49; 1,22</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>250,09%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6,16%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>250,09%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6,16%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,27</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,04</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>0,33</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0,27</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,04</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,66; 0,67</t>
+          <t>-0,66; 1,48</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,02; 1,83</t>
+          <t>-1,02; 0,8</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,2</t>
+          <t>-1,68; 0,67</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 0,56</t>
+          <t>-1,0; 1,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,96; 0,62</t>
+          <t>-0,83; 0,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-0,69; 1,04</t>
+          <t>-0,67; 1,02</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>84,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-13,61%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-50,05%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>49,81%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>84,5%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-13,61%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,35</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0,38</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>-0,38</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>-0,38</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,35</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>0,38</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 0,0</t>
+          <t>0,0; 1,48</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-1,9; 0,0</t>
+          <t>0,0; 1,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,77</t>
+          <t>-2,12; 0,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,44</t>
+          <t>-1,55; 0,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 0,37</t>
+          <t>-0,55; 0,54</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 0,6</t>
+          <t>-0,37; 0,59</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>inf%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>inf%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1061,17 +1061,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>0,37</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>-0,33</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>-0,33</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0,37</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-2,17; 0,0</t>
+          <t>-0,67; 1,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 0,0</t>
+          <t>-1,53; 0,0</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-0,68; 1,72</t>
+          <t>-1,82; 0,0</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-1,69; 0,0</t>
+          <t>-1,42; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,73</t>
+          <t>-0,64; 0,74</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,0</t>
+          <t>-1,15; 0,0</t>
         </is>
       </c>
     </row>
@@ -1137,17 +1137,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>110,99%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>110,99%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>0,5</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>-0,02</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>-0,18</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>0,01</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>0,5</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>-0,02</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 0,21</t>
+          <t>-0,14; 1,22</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,56</t>
+          <t>-0,51; 0,42</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,03; 1,25</t>
+          <t>-0,66; 0,28</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 0,41</t>
+          <t>-0,5; 0,53</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,2; 0,6</t>
+          <t>-0,18; 0,59</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-0,38; 0,32</t>
+          <t>-0,33; 0,37</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>170,87%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>-7,64%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>-48,35%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>2,96%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>170,87%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>-7,64%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1331,17 +1331,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-54,75; 1173,73</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-87,51; 541,62</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-37,87; 1571,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1351,12 +1351,12 @@
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,99; 374,3</t>
+          <t>-41,77; 337,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-72,96; 223,54</t>
+          <t>-71,43; 237,81</t>
         </is>
       </c>
     </row>
